--- a/Matrix_TestCases_V1.xlsx
+++ b/Matrix_TestCases_V1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\OneDrive\Desktop\Repos\qa-evidence-generator\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\OneDrive\Desktop\Repos\evidence-generator-excel-to-word\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152DC521-3E2A-4EAB-90D9-9FC49DF5DCF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5413A0D4-091B-448E-A765-26AAC257AEB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-795" windowWidth="29040" windowHeight="15720" xr2:uid="{753A1B86-19FE-4FFF-989F-9E35BB17853A}"/>
   </bookViews>
